--- a/Viñas Norte - Inventario.xlsx
+++ b/Viñas Norte - Inventario.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>caja 1.42 m² (2 pz)</t>
+          <t>caja 1.4232 m² (2 pz)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>caja 1.36 m² (10 pz)</t>
+          <t>caja 1.35 m² (10 pz)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>caja 1.42 m² (2 pz)</t>
+          <t>caja 1.4232 m² (2 pz)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>caja 1.36 m² (10 pz)</t>
+          <t>caja 1.35 m² (10 pz)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>caja 1.42 m² (2 pz)</t>
+          <t>caja 1.4232 m² (2 pz)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>caja 1.36 m² (10 pz)</t>
+          <t>caja 1.35 m² (10 pz)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
